--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484609_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484609_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9713</v>
+        <v>3.4824</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5148</v>
+        <v>3.0506</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4565</v>
+        <v>0.4317</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2346</v>
@@ -610,13 +610,13 @@
         <v>2.9321</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.5821</v>
+        <v>-2.0711</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9555</v>
+        <v>-0.4196</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.6266</v>
+        <v>-1.6514</v>
       </c>
       <c r="V2" t="n">
         <v>2.8559</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>X. CORTINA CAMPOS</t>
+          <t>J. SAEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.833</v>
+        <v>2.0975</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2997</v>
+        <v>1.8128</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4667</v>
+        <v>0.2847</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3235</v>
+        <v>-0.1098</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7658</v>
+        <v>-1.7192</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5577</v>
+        <v>1.6094</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9514</v>
+        <v>0.3132</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8423</v>
+        <v>-0.4308</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1091</v>
+        <v>0.7441</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3721</v>
+        <v>-0.4231</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0765</v>
+        <v>-1.2884</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4486</v>
+        <v>0.8653</v>
       </c>
       <c r="P3" t="n">
-        <v>0.733</v>
+        <v>2.0158</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6493</v>
+        <v>2.0158</v>
       </c>
       <c r="S3" t="n">
-        <v>0.033</v>
+        <v>-1.3974</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9872</v>
+        <v>-0.0893</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9542</v>
+        <v>-1.3081</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2566</v>
+        <v>1.5889</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2774</v>
+        <v>1.5889</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SAEZ GONZALEZ</t>
+          <t>X. CORTINA CAMPOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5562</v>
+        <v>0.8245</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2219</v>
+        <v>2.4894</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3342</v>
+        <v>-1.6649</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1098</v>
+        <v>2.3235</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7192</v>
+        <v>1.7658</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6094</v>
+        <v>0.5577</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3132</v>
+        <v>1.9514</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4308</v>
+        <v>1.8423</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7441</v>
+        <v>0.1091</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4231</v>
+        <v>0.3721</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2884</v>
+        <v>-0.0765</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8653</v>
+        <v>0.4486</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0158</v>
+        <v>0.733</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0158</v>
+        <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9388</v>
+        <v>-0.9755</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6802</v>
+        <v>0.1769</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2585</v>
+        <v>-1.1524</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5889</v>
+        <v>-1.2566</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5889</v>
+        <v>1.2774</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SÁEZ GONZÁLEZ</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3251</v>
+        <v>0.6516</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3251</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.5966</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3251</v>
+        <v>-2.8889</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3251</v>
+        <v>-3.5846</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.6957</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3251</v>
+        <v>-1.8323</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3251</v>
+        <v>-1.9513</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.119</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.0566</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1.6333</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.5768</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.7489</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-1.4387</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.7304</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.7084</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>3.1466</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.6127</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. PALOMARES MONZO</t>
+          <t>J. SÁEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1344</v>
+        <v>0.3251</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1018</v>
+        <v>0.3251</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0326</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3273</v>
+        <v>0.3251</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1895</v>
+        <v>0.3251</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1378</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0633</v>
+        <v>0.3251</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0217</v>
+        <v>0.3251</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0417</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.264</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1679</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0961</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6449</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1652</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4798</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CASADO SEGURA</t>
+          <t>P. PALOMARES MONZO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1858</v>
+        <v>-0.0298</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5284</v>
+        <v>-0.0468</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7141</v>
+        <v>0.017</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5782</v>
+        <v>0.3273</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.983</v>
+        <v>0.1895</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5612</v>
+        <v>0.1378</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3247</v>
+        <v>0.0633</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3402</v>
+        <v>0.0217</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9845</v>
+        <v>0.0417</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7465</v>
+        <v>0.264</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.3232</v>
+        <v>0.1679</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5768</v>
+        <v>0.0961</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0995</v>
+        <v>0.1833</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5656</v>
+        <v>0.1833</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6095</v>
+        <v>-0.5403</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6018</v>
+        <v>-0.1101</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.2113</v>
+        <v>-0.4302</v>
       </c>
       <c r="V7" t="n">
-        <v>0.945</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>J. CASADO SEGURA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4155</v>
+        <v>-0.4107</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.591</v>
+        <v>0.2539</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1755</v>
+        <v>-0.6646</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.8889</v>
+        <v>0.5782</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.5846</v>
+        <v>-1.983</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6957</v>
+        <v>2.5612</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.8323</v>
+        <v>2.3247</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.9513</v>
+        <v>0.3402</v>
       </c>
       <c r="L8" t="n">
-        <v>0.119</v>
+        <v>1.9845</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0566</v>
+        <v>-1.7465</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6333</v>
+        <v>-2.3232</v>
       </c>
       <c r="O8" t="n">
         <v>0.5768</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8326</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7489</v>
+        <v>2.5656</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.5058</v>
+        <v>-0.8345</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3763</v>
+        <v>0.3273</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1295</v>
+        <v>-1.1618</v>
       </c>
       <c r="V8" t="n">
-        <v>3.1466</v>
+        <v>0.945</v>
       </c>
       <c r="W8" t="n">
-        <v>2.5339</v>
+        <v>1.267</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6127</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7587</v>
+        <v>-1.0085</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5686</v>
+        <v>-1.8431</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8099</v>
+        <v>0.8346</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3974</v>
@@ -1156,13 +1156,13 @@
         <v>1.4661</v>
       </c>
       <c r="S9" t="n">
-        <v>0.08890000000000001</v>
+        <v>-0.1608</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0746</v>
+        <v>-0.3492</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1636</v>
+        <v>0.1883</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5035</v>
+        <v>-2.5744</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9755</v>
+        <v>-2.1949</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5281</v>
+        <v>-0.3794</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9859</v>
@@ -1234,13 +1234,13 @@
         <v>2.1991</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.324</v>
+        <v>-0.3948</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7119</v>
+        <v>0.4925</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0359</v>
+        <v>-0.8873</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6439</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. ROIG ARINO</t>
+          <t>J. DEL MORAL GALLARDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0094</v>
+        <v>-2.6748</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7708</v>
+        <v>-2.0375</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2387</v>
+        <v>-0.6374</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9019</v>
+        <v>-2.6977</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3794</v>
+        <v>-0.9989</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4775</v>
+        <v>-1.6988</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4299</v>
+        <v>-2.174</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0861</v>
+        <v>-0.2509</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.516</v>
+        <v>-1.9231</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4719</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4655</v>
+        <v>-0.748</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9935</v>
+        <v>0.2243</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8326</v>
+        <v>0.5498</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.6651</v>
+        <v>0.5498</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1392</v>
+        <v>-0.527</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4917</v>
+        <v>0.1365</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.631</v>
+        <v>-0.6635</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.8009</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.8009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. DEL MORAL GALLARDO</t>
+          <t>T. ROIG ARINO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2986</v>
+        <v>-3.6308</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6694</v>
+        <v>-2.0453</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6291</v>
+        <v>-1.5855</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.6977</v>
+        <v>-0.9019</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9989</v>
+        <v>-1.3794</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6988</v>
+        <v>0.4775</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.174</v>
+        <v>-0.4299</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2509</v>
+        <v>0.0861</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9231</v>
+        <v>-0.516</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.4719</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.748</v>
+        <v>-1.4655</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2243</v>
+        <v>0.9935</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5498</v>
+        <v>1.8326</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5498</v>
+        <v>3.6651</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1507</v>
+        <v>-0.7606000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4955</v>
+        <v>0.2172</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6552</v>
+        <v>-0.9778</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-3.8009</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-3.8009</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9985</v>
+        <v>-3.9187</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5256</v>
+        <v>-2.4705</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4729</v>
+        <v>-1.4482</v>
       </c>
       <c r="G13" t="n">
         <v>-0.9517</v>
@@ -1468,13 +1468,13 @@
         <v>0.733</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6803</v>
+        <v>-0.6005</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4404</v>
+        <v>-0.3854</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2399</v>
+        <v>-0.2151</v>
       </c>
       <c r="V13" t="n">
         <v>-1.267</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.1041</v>
+        <v>-5.714</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.3133</v>
+        <v>-3.8737</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7908</v>
+        <v>-1.8404</v>
       </c>
       <c r="G14" t="n">
         <v>-4.3826</v>
@@ -1546,13 +1546,13 @@
         <v>0.3665</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.431</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5505</v>
+        <v>-0.1108</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2706</v>
+        <v>-0.3201</v>
       </c>
       <c r="V14" t="n">
         <v>-1.267</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-13.7229</v>
+        <v>-12.5806</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.626099999999999</v>
+        <v>-7.5251</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.0969</v>
+        <v>-5.0558</v>
       </c>
       <c r="G15" t="n">
         <v>-10.9964</v>
@@ -1603,7 +1603,7 @@
         <v>-4.6539</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3228999999999995</v>
+        <v>0.3229000000000004</v>
       </c>
       <c r="M15" t="n">
         <v>-6.665299999999998</v>
@@ -1612,10 +1612,10 @@
         <v>-11.9525</v>
       </c>
       <c r="O15" t="n">
-        <v>5.2875</v>
+        <v>5.287499999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>8.246699999999999</v>
+        <v>8.246700000000001</v>
       </c>
       <c r="Q15" t="n">
         <v>-12.8281</v>
@@ -1624,13 +1624,13 @@
         <v>21.0746</v>
       </c>
       <c r="S15" t="n">
-        <v>-11.2745</v>
+        <v>-10.1322</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.9456</v>
+        <v>-0.8444000000000004</v>
       </c>
       <c r="U15" t="n">
-        <v>-9.328900000000001</v>
+        <v>-9.287799999999999</v>
       </c>
       <c r="V15" t="n">
         <v>0.3009999999999997</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>11.238</v>
+        <v>11.563</v>
       </c>
       <c r="E16" t="n">
-        <v>7.966</v>
+        <v>7.8698</v>
       </c>
       <c r="F16" t="n">
-        <v>3.272</v>
+        <v>3.6931</v>
       </c>
       <c r="G16" t="n">
         <v>7.3426</v>
@@ -1702,13 +1702,13 @@
         <v>2.5656</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5447</v>
+        <v>1.8697</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4819</v>
+        <v>1.3858</v>
       </c>
       <c r="U16" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.4839</v>
       </c>
       <c r="V16" t="n">
         <v>2.5339</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>9.3819</v>
+        <v>5.7599</v>
       </c>
       <c r="E17" t="n">
-        <v>7.1998</v>
+        <v>4.1229</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1821</v>
+        <v>1.6371</v>
       </c>
       <c r="G17" t="n">
         <v>0.2376</v>
@@ -1780,13 +1780,13 @@
         <v>1.0995</v>
       </c>
       <c r="S17" t="n">
-        <v>7.3146</v>
+        <v>3.6927</v>
       </c>
       <c r="T17" t="n">
-        <v>5.9691</v>
+        <v>2.8922</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3455</v>
+        <v>0.8005</v>
       </c>
       <c r="V17" t="n">
         <v>3.479</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4385</v>
+        <v>3.6856</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8626</v>
+        <v>3.2087</v>
       </c>
       <c r="F18" t="n">
-        <v>0.576</v>
+        <v>0.4769</v>
       </c>
       <c r="G18" t="n">
         <v>1.9695</v>
@@ -1858,13 +1858,13 @@
         <v>2.1991</v>
       </c>
       <c r="S18" t="n">
-        <v>0.998</v>
+        <v>2.2451</v>
       </c>
       <c r="T18" t="n">
-        <v>0.218</v>
+        <v>1.5641</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7801</v>
+        <v>0.681</v>
       </c>
       <c r="V18" t="n">
         <v>0.0208</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MICHAEL KING</t>
+          <t>L. SALVADOR MONTANES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1561</v>
+        <v>1.183</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4939</v>
+        <v>-0.224</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6501</v>
+        <v>1.407</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4401</v>
+        <v>-1.269</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1741</v>
+        <v>-0.1756</v>
       </c>
       <c r="I19" t="n">
-        <v>0.266</v>
+        <v>-1.0934</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6328</v>
+        <v>-1.0303</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5911</v>
+        <v>-0.5143</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0417</v>
+        <v>-0.516</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8072</v>
+        <v>-0.2388</v>
       </c>
       <c r="N19" t="n">
-        <v>0.583</v>
+        <v>0.3386</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2243</v>
+        <v>-0.5774</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3665</v>
+        <v>0.3665</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4661</v>
+        <v>2.1991</v>
       </c>
       <c r="S19" t="n">
-        <v>0.08260000000000001</v>
+        <v>1.7739</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3839</v>
+        <v>1.3718</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3013</v>
+        <v>0.4021</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3115</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3219</v>
+        <v>1.267</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3219</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDÉS</t>
+          <t>D. MICHAEL KING</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9502</v>
+        <v>0.9915</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9502</v>
+        <v>-0.7824</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1.7739</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9502</v>
+        <v>1.4401</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3251</v>
+        <v>1.1741</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6251</v>
+        <v>0.266</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9502</v>
+        <v>0.6328</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3251</v>
+        <v>0.5911</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6251</v>
+        <v>0.0417</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>0.8072</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>0.583</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.2243</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-0.082</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.0954</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.1774</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. SALVADOR MONTANES</t>
+          <t>E. NAVARRO VALDÉS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.153</v>
+        <v>0.9502</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3779</v>
+        <v>0.9502</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5309</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.269</v>
+        <v>0.9502</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1756</v>
+        <v>0.3251</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0934</v>
+        <v>0.6251</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0303</v>
+        <v>0.9502</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5143</v>
+        <v>0.3251</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.516</v>
+        <v>0.6251</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2388</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3386</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5774</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1991</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7439</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.218</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.526</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4173</v>
+        <v>-0.7801</v>
       </c>
       <c r="E22" t="n">
-        <v>0.363</v>
+        <v>0.0746</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7803</v>
+        <v>-0.8547</v>
       </c>
       <c r="G22" t="n">
         <v>0.3856</v>
@@ -2170,13 +2170,13 @@
         <v>0.3665</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7023</v>
+        <v>0.3395</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9698</v>
+        <v>0.6814</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2675</v>
+        <v>-0.3418</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9554</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. ROMAN MORA</t>
+          <t>D. CHALATASHVILI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1832</v>
+        <v>-0.8789</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7845</v>
+        <v>-2.3904</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3986</v>
+        <v>1.5115</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1499</v>
+        <v>-0.8335</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6627</v>
+        <v>1.6667</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5128</v>
+        <v>-2.5002</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6194</v>
+        <v>-1.0469</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0217</v>
+        <v>1.5172</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.641</v>
+        <v>-2.5641</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7692</v>
+        <v>0.2134</v>
       </c>
       <c r="N23" t="n">
-        <v>0.641</v>
+        <v>0.1495</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1282</v>
+        <v>0.064</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.06610000000000001</v>
+        <v>1.0541</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1652</v>
+        <v>0.4891</v>
       </c>
       <c r="U23" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. CHALATASHVILI</t>
+          <t>F. ROMAN MORA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4281</v>
+        <v>-1.0345</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0635</v>
+        <v>-0.7845</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6353</v>
+        <v>-0.25</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8335</v>
+        <v>0.1499</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6667</v>
+        <v>0.6627</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.5002</v>
+        <v>-0.5128</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0469</v>
+        <v>-0.6194</v>
       </c>
       <c r="K24" t="n">
-        <v>1.5172</v>
+        <v>0.0217</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.5641</v>
+        <v>-0.641</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2134</v>
+        <v>0.7692</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1495</v>
+        <v>0.641</v>
       </c>
       <c r="O24" t="n">
-        <v>0.064</v>
+        <v>0.1282</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5049</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.184</v>
+        <v>-0.1652</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6889</v>
+        <v>0.2477</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.7163</v>
+        <v>-1.8343</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.8539</v>
+        <v>-2.0462</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1376</v>
+        <v>0.2119</v>
       </c>
       <c r="G25" t="n">
         <v>0.7477</v>
@@ -2404,13 +2404,13 @@
         <v>0.5498</v>
       </c>
       <c r="S25" t="n">
-        <v>1.002</v>
+        <v>0.884</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7866</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2154</v>
+        <v>0.2898</v>
       </c>
       <c r="V25" t="n">
         <v>-1.267</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.9732</v>
+        <v>-2.0058</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.7833</v>
+        <v>-3.0141</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8101</v>
+        <v>1.0083</v>
       </c>
       <c r="G26" t="n">
         <v>0.0849</v>
@@ -2482,13 +2482,13 @@
         <v>1.6493</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9848</v>
+        <v>-0.0174</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2941</v>
+        <v>0.4751</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6907</v>
+        <v>-0.4925</v>
       </c>
       <c r="V26" t="n">
         <v>-1.89</v>
@@ -2596,10 +2596,10 @@
         <v>13.723</v>
       </c>
       <c r="E28" t="n">
-        <v>5.097000000000002</v>
+        <v>5.097</v>
       </c>
       <c r="F28" t="n">
-        <v>8.626200000000001</v>
+        <v>8.625999999999999</v>
       </c>
       <c r="G28" t="n">
         <v>10.9964</v>
@@ -2626,10 +2626,10 @@
         <v>4.6539</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.3226</v>
+        <v>-0.3226000000000002</v>
       </c>
       <c r="P28" t="n">
-        <v>-8.246700000000001</v>
+        <v>-8.246699999999999</v>
       </c>
       <c r="Q28" t="n">
         <v>-21.0749</v>
@@ -2638,16 +2638,16 @@
         <v>12.828</v>
       </c>
       <c r="S28" t="n">
-        <v>11.2742</v>
+        <v>11.2743</v>
       </c>
       <c r="T28" t="n">
-        <v>9.328900000000003</v>
+        <v>9.328899999999999</v>
       </c>
       <c r="U28" t="n">
         <v>1.9455</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.301199999999999</v>
+        <v>-0.3011999999999999</v>
       </c>
       <c r="W28" t="n">
         <v>10.1773</v>
